--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119850872</v>
+        <v>119849502</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>91182</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,47 +1032,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626667</v>
+        <v>626696</v>
       </c>
       <c r="R5" t="n">
-        <v>6897628</v>
+        <v>6897732</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119849502</v>
+        <v>119850872</v>
       </c>
       <c r="B6" t="n">
-        <v>91182</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,38 +1144,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626696</v>
+        <v>626667</v>
       </c>
       <c r="R6" t="n">
-        <v>6897732</v>
+        <v>6897628</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1849,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119848698</v>
+        <v>119848797</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,25 +1861,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626565</v>
+        <v>626642</v>
       </c>
       <c r="R12" t="n">
-        <v>6897628</v>
+        <v>6897655</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119848797</v>
+        <v>119848698</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,25 +1973,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626642</v>
+        <v>626565</v>
       </c>
       <c r="R13" t="n">
-        <v>6897655</v>
+        <v>6897628</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -1849,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119848797</v>
+        <v>119848698</v>
       </c>
       <c r="B12" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,25 +1861,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626642</v>
+        <v>626565</v>
       </c>
       <c r="R12" t="n">
-        <v>6897655</v>
+        <v>6897628</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119848698</v>
+        <v>119848797</v>
       </c>
       <c r="B13" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,25 +1973,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626565</v>
+        <v>626642</v>
       </c>
       <c r="R13" t="n">
-        <v>6897628</v>
+        <v>6897655</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119849729</v>
+        <v>119848811</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>57463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626771</v>
+        <v>626637</v>
       </c>
       <c r="R2" t="n">
-        <v>6897796</v>
+        <v>6897656</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119848966</v>
+        <v>119848727</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626602</v>
+        <v>626573</v>
       </c>
       <c r="R3" t="n">
-        <v>6897710</v>
+        <v>6897625</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119849031</v>
+        <v>119849022</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -934,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -944,14 +953,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626550</v>
+        <v>626600</v>
       </c>
       <c r="R4" t="n">
-        <v>6897759</v>
+        <v>6897718</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119849502</v>
+        <v>119849799</v>
       </c>
       <c r="B5" t="n">
-        <v>91182</v>
+        <v>90527</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1045,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626696</v>
+        <v>626805</v>
       </c>
       <c r="R5" t="n">
-        <v>6897732</v>
+        <v>6897774</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1132,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119850872</v>
+        <v>119850449</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1177,14 +1186,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626667</v>
+        <v>626682</v>
       </c>
       <c r="R6" t="n">
-        <v>6897628</v>
+        <v>6897973</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119850449</v>
+        <v>119849502</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>91182</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,47 +1274,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626682</v>
+        <v>626696</v>
       </c>
       <c r="R7" t="n">
-        <v>6897973</v>
+        <v>6897732</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119848811</v>
+        <v>119850872</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,50 +1386,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626637</v>
+        <v>626667</v>
       </c>
       <c r="R8" t="n">
-        <v>6897656</v>
+        <v>6897628</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,7 +1495,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119848932</v>
+        <v>119848788</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626605</v>
+        <v>626654</v>
       </c>
       <c r="R9" t="n">
-        <v>6897688</v>
+        <v>6897634</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119848807</v>
+        <v>119848797</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,25 +1628,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626637</v>
+        <v>626642</v>
       </c>
       <c r="R10" t="n">
-        <v>6897656</v>
+        <v>6897655</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119849022</v>
+        <v>119848966</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,47 +1740,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626600</v>
+        <v>626602</v>
       </c>
       <c r="R11" t="n">
-        <v>6897718</v>
+        <v>6897710</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1812,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1849,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119848698</v>
+        <v>119849743</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,25 +1852,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626565</v>
+        <v>626771</v>
       </c>
       <c r="R12" t="n">
-        <v>6897628</v>
+        <v>6897796</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1924,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119848797</v>
+        <v>119848698</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,25 +1964,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2001,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626642</v>
+        <v>626565</v>
       </c>
       <c r="R13" t="n">
-        <v>6897655</v>
+        <v>6897628</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2036,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119850843</v>
+        <v>119849763</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,25 +2076,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2113,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626698</v>
+        <v>626771</v>
       </c>
       <c r="R14" t="n">
-        <v>6897755</v>
+        <v>6897796</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2148,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,10 +2176,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119848727</v>
+        <v>119850843</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,25 +2188,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2225,10 +2216,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626573</v>
+        <v>626698</v>
       </c>
       <c r="R15" t="n">
-        <v>6897625</v>
+        <v>6897755</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2260,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119849743</v>
+        <v>119848932</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2309,38 +2300,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626771</v>
+        <v>626605</v>
       </c>
       <c r="R16" t="n">
-        <v>6897796</v>
+        <v>6897688</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119849799</v>
+        <v>119848807</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626805</v>
+        <v>626637</v>
       </c>
       <c r="R17" t="n">
-        <v>6897774</v>
+        <v>6897656</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,7 +2521,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119848788</v>
+        <v>119849031</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2566,14 +2566,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626654</v>
+        <v>626550</v>
       </c>
       <c r="R18" t="n">
-        <v>6897634</v>
+        <v>6897759</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -1495,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119848788</v>
+        <v>119848797</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,47 +1507,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626654</v>
+        <v>626642</v>
       </c>
       <c r="R9" t="n">
-        <v>6897634</v>
+        <v>6897655</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1616,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119848797</v>
+        <v>119848788</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,38 +1619,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626642</v>
+        <v>626654</v>
       </c>
       <c r="R10" t="n">
-        <v>6897655</v>
+        <v>6897634</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119848966</v>
+        <v>119849743</v>
       </c>
       <c r="B11" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,21 +1744,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626602</v>
+        <v>626771</v>
       </c>
       <c r="R11" t="n">
-        <v>6897710</v>
+        <v>6897796</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119849743</v>
+        <v>119848698</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>90527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,25 +1852,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626771</v>
+        <v>626565</v>
       </c>
       <c r="R12" t="n">
-        <v>6897796</v>
+        <v>6897628</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119848698</v>
+        <v>119848966</v>
       </c>
       <c r="B13" t="n">
-        <v>90527</v>
+        <v>90846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626565</v>
+        <v>626602</v>
       </c>
       <c r="R13" t="n">
-        <v>6897628</v>
+        <v>6897710</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119848811</v>
+        <v>119850449</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
+          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626637</v>
+        <v>626682</v>
       </c>
       <c r="R2" t="n">
-        <v>6897656</v>
+        <v>6897973</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119848727</v>
+        <v>119848797</v>
       </c>
       <c r="B3" t="n">
         <v>90562</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626573</v>
+        <v>626642</v>
       </c>
       <c r="R3" t="n">
-        <v>6897625</v>
+        <v>6897655</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119849022</v>
+        <v>119848788</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626600</v>
+        <v>626654</v>
       </c>
       <c r="R4" t="n">
-        <v>6897718</v>
+        <v>6897634</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119849799</v>
+        <v>119849763</v>
       </c>
       <c r="B5" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,25 +1041,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626805</v>
+        <v>626771</v>
       </c>
       <c r="R5" t="n">
-        <v>6897774</v>
+        <v>6897796</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119850449</v>
+        <v>119848811</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,50 +1153,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
+          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626682</v>
+        <v>626637</v>
       </c>
       <c r="R6" t="n">
-        <v>6897973</v>
+        <v>6897656</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119849502</v>
+        <v>119848932</v>
       </c>
       <c r="B7" t="n">
-        <v>91182</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,38 +1274,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626696</v>
+        <v>626605</v>
       </c>
       <c r="R7" t="n">
-        <v>6897732</v>
+        <v>6897688</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119850872</v>
+        <v>119849799</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,47 +1395,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626667</v>
+        <v>626805</v>
       </c>
       <c r="R8" t="n">
-        <v>6897628</v>
+        <v>6897774</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119848797</v>
+        <v>119849022</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,38 +1507,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626642</v>
+        <v>626600</v>
       </c>
       <c r="R9" t="n">
-        <v>6897655</v>
+        <v>6897718</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1570,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119848788</v>
+        <v>119849502</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>91182</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,47 +1628,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626654</v>
+        <v>626696</v>
       </c>
       <c r="R10" t="n">
-        <v>6897634</v>
+        <v>6897732</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119849743</v>
+        <v>119848698</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>90527</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,25 +1740,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626771</v>
+        <v>626565</v>
       </c>
       <c r="R11" t="n">
-        <v>6897796</v>
+        <v>6897628</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119848698</v>
+        <v>119849031</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,38 +1852,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626565</v>
+        <v>626550</v>
       </c>
       <c r="R12" t="n">
-        <v>6897628</v>
+        <v>6897759</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1915,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119848966</v>
+        <v>119849743</v>
       </c>
       <c r="B13" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,21 +1977,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,10 +2001,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626602</v>
+        <v>626771</v>
       </c>
       <c r="R13" t="n">
-        <v>6897710</v>
+        <v>6897796</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2027,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2046,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119849763</v>
+        <v>119850843</v>
       </c>
       <c r="B14" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,25 +2085,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2104,10 +2113,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626771</v>
+        <v>626698</v>
       </c>
       <c r="R14" t="n">
-        <v>6897796</v>
+        <v>6897755</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2139,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,7 +2185,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119850843</v>
+        <v>119850872</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2209,17 +2218,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626698</v>
+        <v>626667</v>
       </c>
       <c r="R15" t="n">
-        <v>6897755</v>
+        <v>6897628</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2251,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,10 +2306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119848932</v>
+        <v>119848727</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,47 +2318,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626605</v>
+        <v>626573</v>
       </c>
       <c r="R16" t="n">
-        <v>6897688</v>
+        <v>6897625</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2372,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2521,10 +2530,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119849031</v>
+        <v>119848966</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2533,47 +2542,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626550</v>
+        <v>626602</v>
       </c>
       <c r="R18" t="n">
-        <v>6897759</v>
+        <v>6897710</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119849502</v>
+        <v>119848698</v>
       </c>
       <c r="B10" t="n">
-        <v>91182</v>
+        <v>90527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,21 +1632,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626696</v>
+        <v>626565</v>
       </c>
       <c r="R10" t="n">
-        <v>6897732</v>
+        <v>6897628</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119848698</v>
+        <v>119849502</v>
       </c>
       <c r="B11" t="n">
-        <v>90527</v>
+        <v>91182</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,21 +1744,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626565</v>
+        <v>626696</v>
       </c>
       <c r="R11" t="n">
-        <v>6897628</v>
+        <v>6897732</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119850449</v>
+        <v>119850872</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -720,14 +720,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626682</v>
+        <v>626667</v>
       </c>
       <c r="R2" t="n">
-        <v>6897973</v>
+        <v>6897628</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119848797</v>
+        <v>119849022</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +808,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626642</v>
+        <v>626600</v>
       </c>
       <c r="R3" t="n">
-        <v>6897655</v>
+        <v>6897718</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119848788</v>
+        <v>119848811</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,50 +929,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626654</v>
+        <v>626637</v>
       </c>
       <c r="R4" t="n">
-        <v>6897634</v>
+        <v>6897656</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119849763</v>
+        <v>119849729</v>
       </c>
       <c r="B5" t="n">
         <v>90562</v>
@@ -1141,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119848811</v>
+        <v>119848788</v>
       </c>
       <c r="B6" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,50 +1162,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626637</v>
+        <v>626654</v>
       </c>
       <c r="R6" t="n">
-        <v>6897656</v>
+        <v>6897634</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,7 +1271,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119848932</v>
+        <v>119850843</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1295,26 +1304,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626605</v>
+        <v>626698</v>
       </c>
       <c r="R7" t="n">
-        <v>6897688</v>
+        <v>6897755</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119849799</v>
+        <v>119850449</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,38 +1395,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626805</v>
+        <v>626682</v>
       </c>
       <c r="R8" t="n">
-        <v>6897774</v>
+        <v>6897973</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119849022</v>
+        <v>119848797</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,47 +1516,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626600</v>
+        <v>626642</v>
       </c>
       <c r="R9" t="n">
-        <v>6897718</v>
+        <v>6897655</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119848698</v>
+        <v>119848727</v>
       </c>
       <c r="B10" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,25 +1628,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626565</v>
+        <v>626573</v>
       </c>
       <c r="R10" t="n">
-        <v>6897628</v>
+        <v>6897625</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119850843</v>
+        <v>119849799</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626698</v>
+        <v>626805</v>
       </c>
       <c r="R14" t="n">
-        <v>6897755</v>
+        <v>6897774</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119850872</v>
+        <v>119848966</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,47 +2197,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626667</v>
+        <v>626602</v>
       </c>
       <c r="R15" t="n">
-        <v>6897628</v>
+        <v>6897710</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2269,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119848727</v>
+        <v>119848932</v>
       </c>
       <c r="B16" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,38 +2309,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626573</v>
+        <v>626605</v>
       </c>
       <c r="R16" t="n">
-        <v>6897625</v>
+        <v>6897688</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,10 +2418,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119848807</v>
+        <v>119848698</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,25 +2430,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626637</v>
+        <v>626565</v>
       </c>
       <c r="R17" t="n">
-        <v>6897656</v>
+        <v>6897628</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2530,10 +2530,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119848966</v>
+        <v>119848807</v>
       </c>
       <c r="B18" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,25 +2542,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626602</v>
+        <v>626637</v>
       </c>
       <c r="R18" t="n">
-        <v>6897710</v>
+        <v>6897656</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -2185,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119848966</v>
+        <v>119848932</v>
       </c>
       <c r="B15" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,38 +2197,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626602</v>
+        <v>626605</v>
       </c>
       <c r="R15" t="n">
-        <v>6897710</v>
+        <v>6897688</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2260,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,10 +2306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119848932</v>
+        <v>119848698</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2309,47 +2318,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626605</v>
+        <v>626565</v>
       </c>
       <c r="R16" t="n">
-        <v>6897688</v>
+        <v>6897628</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,10 +2418,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119848698</v>
+        <v>119848966</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>90846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,25 +2430,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626565</v>
+        <v>626602</v>
       </c>
       <c r="R17" t="n">
-        <v>6897628</v>
+        <v>6897710</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -2185,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119848932</v>
+        <v>119848966</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,47 +2197,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626605</v>
+        <v>626602</v>
       </c>
       <c r="R15" t="n">
-        <v>6897688</v>
+        <v>6897710</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2269,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119848698</v>
+        <v>119848932</v>
       </c>
       <c r="B16" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,38 +2309,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626565</v>
+        <v>626605</v>
       </c>
       <c r="R16" t="n">
-        <v>6897628</v>
+        <v>6897688</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,10 +2418,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119848966</v>
+        <v>119848698</v>
       </c>
       <c r="B17" t="n">
-        <v>90846</v>
+        <v>90527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,25 +2430,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626602</v>
+        <v>626565</v>
       </c>
       <c r="R17" t="n">
-        <v>6897710</v>
+        <v>6897628</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119849502</v>
+        <v>119849031</v>
       </c>
       <c r="B11" t="n">
-        <v>91182</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,38 +1740,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626696</v>
+        <v>626550</v>
       </c>
       <c r="R11" t="n">
-        <v>6897732</v>
+        <v>6897759</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1803,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1822,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119849031</v>
+        <v>119849743</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,47 +1861,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626550</v>
+        <v>626771</v>
       </c>
       <c r="R12" t="n">
-        <v>6897759</v>
+        <v>6897796</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119849743</v>
+        <v>119849799</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>90527</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,25 +1973,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626771</v>
+        <v>626805</v>
       </c>
       <c r="R13" t="n">
-        <v>6897796</v>
+        <v>6897774</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119849799</v>
+        <v>119848932</v>
       </c>
       <c r="B14" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,38 +2085,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626805</v>
+        <v>626605</v>
       </c>
       <c r="R14" t="n">
-        <v>6897774</v>
+        <v>6897688</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2148,7 +2157,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2167,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119848932</v>
+        <v>119848698</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,47 +2206,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626605</v>
+        <v>626565</v>
       </c>
       <c r="R15" t="n">
-        <v>6897688</v>
+        <v>6897628</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,10 +2306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119848698</v>
+        <v>119848966</v>
       </c>
       <c r="B16" t="n">
-        <v>90527</v>
+        <v>90846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,25 +2318,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2346,10 +2346,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626565</v>
+        <v>626602</v>
       </c>
       <c r="R16" t="n">
-        <v>6897628</v>
+        <v>6897710</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,10 +2418,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119848966</v>
+        <v>119848807</v>
       </c>
       <c r="B17" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,25 +2430,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626602</v>
+        <v>626637</v>
       </c>
       <c r="R17" t="n">
-        <v>6897710</v>
+        <v>6897656</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2530,10 +2530,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119848807</v>
+        <v>119870499</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>91175</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2546,34 +2546,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626637</v>
+        <v>626602</v>
       </c>
       <c r="R18" t="n">
-        <v>6897656</v>
+        <v>6897691</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2603,27 +2606,18 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2642,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119870499</v>
+        <v>119849502</v>
       </c>
       <c r="B19" t="n">
-        <v>91175</v>
+        <v>91200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2654,41 +2648,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>483</v>
+        <v>1339</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Älgmyran, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626602</v>
+        <v>626696</v>
       </c>
       <c r="R19" t="n">
-        <v>6897691</v>
+        <v>6897732</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2718,18 +2709,27 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119850872</v>
+        <v>119848788</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626667</v>
+        <v>626654</v>
       </c>
       <c r="R2" t="n">
-        <v>6897628</v>
+        <v>6897634</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119849022</v>
+        <v>119848727</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,47 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626600</v>
+        <v>626573</v>
       </c>
       <c r="R3" t="n">
-        <v>6897718</v>
+        <v>6897625</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119848811</v>
+        <v>119849743</v>
       </c>
       <c r="B4" t="n">
-        <v>57463</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,46 +924,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626637</v>
+        <v>626771</v>
       </c>
       <c r="R4" t="n">
-        <v>6897656</v>
+        <v>6897796</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119849729</v>
+        <v>119848932</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,38 +1032,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626771</v>
+        <v>626605</v>
       </c>
       <c r="R5" t="n">
-        <v>6897796</v>
+        <v>6897688</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119848788</v>
+        <v>119849031</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,7 +1176,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1195,14 +1186,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626654</v>
+        <v>626550</v>
       </c>
       <c r="R6" t="n">
-        <v>6897634</v>
+        <v>6897759</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1234,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119850843</v>
+        <v>119849729</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,25 +1274,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626698</v>
+        <v>626771</v>
       </c>
       <c r="R7" t="n">
-        <v>6897755</v>
+        <v>6897796</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119850449</v>
+        <v>119848797</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,47 +1386,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626682</v>
+        <v>626642</v>
       </c>
       <c r="R8" t="n">
-        <v>6897973</v>
+        <v>6897655</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1467,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119848797</v>
+        <v>119848807</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,25 +1498,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1544,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626642</v>
+        <v>626637</v>
       </c>
       <c r="R9" t="n">
-        <v>6897655</v>
+        <v>6897656</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1579,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119848727</v>
+        <v>119849022</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,38 +1610,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626573</v>
+        <v>626600</v>
       </c>
       <c r="R10" t="n">
-        <v>6897625</v>
+        <v>6897718</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1691,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119849031</v>
+        <v>119848966</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>90864</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,47 +1731,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626550</v>
+        <v>626602</v>
       </c>
       <c r="R11" t="n">
-        <v>6897759</v>
+        <v>6897710</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1812,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,7 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1849,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119849743</v>
+        <v>119850449</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,38 +1843,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626771</v>
+        <v>626682</v>
       </c>
       <c r="R12" t="n">
-        <v>6897796</v>
+        <v>6897973</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1924,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119849799</v>
+        <v>119848811</v>
       </c>
       <c r="B13" t="n">
-        <v>90527</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,41 +1964,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626805</v>
+        <v>626637</v>
       </c>
       <c r="R13" t="n">
-        <v>6897774</v>
+        <v>6897656</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119848932</v>
+        <v>119848698</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>90545</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,47 +2085,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626605</v>
+        <v>626565</v>
       </c>
       <c r="R14" t="n">
-        <v>6897688</v>
+        <v>6897628</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2157,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2167,7 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2194,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119848698</v>
+        <v>119850843</v>
       </c>
       <c r="B15" t="n">
-        <v>90527</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,25 +2197,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2234,10 +2225,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626565</v>
+        <v>626698</v>
       </c>
       <c r="R15" t="n">
-        <v>6897628</v>
+        <v>6897755</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2269,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119848966</v>
+        <v>119849799</v>
       </c>
       <c r="B16" t="n">
-        <v>90846</v>
+        <v>90545</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,25 +2309,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2346,10 +2337,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626602</v>
+        <v>626805</v>
       </c>
       <c r="R16" t="n">
-        <v>6897710</v>
+        <v>6897774</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2381,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119848807</v>
+        <v>119850872</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2451,17 +2442,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626637</v>
+        <v>626667</v>
       </c>
       <c r="R17" t="n">
-        <v>6897656</v>
+        <v>6897628</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2533,7 +2533,7 @@
         <v>119870499</v>
       </c>
       <c r="B18" t="n">
-        <v>91175</v>
+        <v>91193</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119848788</v>
+        <v>119848932</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626654</v>
+        <v>626605</v>
       </c>
       <c r="R2" t="n">
-        <v>6897634</v>
+        <v>6897688</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119848727</v>
+        <v>119850449</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +808,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626573</v>
+        <v>626682</v>
       </c>
       <c r="R3" t="n">
-        <v>6897625</v>
+        <v>6897973</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119849743</v>
+        <v>119849799</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626771</v>
+        <v>626805</v>
       </c>
       <c r="R4" t="n">
-        <v>6897796</v>
+        <v>6897774</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1020,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119848932</v>
+        <v>119848807</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1053,26 +1062,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626605</v>
+        <v>626637</v>
       </c>
       <c r="R5" t="n">
-        <v>6897688</v>
+        <v>6897656</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119849031</v>
+        <v>119848727</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,47 +1153,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626550</v>
+        <v>626573</v>
       </c>
       <c r="R6" t="n">
-        <v>6897759</v>
+        <v>6897625</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119849729</v>
+        <v>119848966</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,21 +1269,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626771</v>
+        <v>626602</v>
       </c>
       <c r="R7" t="n">
-        <v>6897796</v>
+        <v>6897710</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119848797</v>
+        <v>119849743</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626642</v>
+        <v>626771</v>
       </c>
       <c r="R8" t="n">
-        <v>6897655</v>
+        <v>6897796</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1449,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,7 +1477,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119848807</v>
+        <v>119848788</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1519,17 +1510,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626637</v>
+        <v>626654</v>
       </c>
       <c r="R9" t="n">
-        <v>6897656</v>
+        <v>6897634</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,7 +1598,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119849022</v>
+        <v>119850843</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1631,26 +1631,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626600</v>
+        <v>626698</v>
       </c>
       <c r="R10" t="n">
-        <v>6897718</v>
+        <v>6897755</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119848966</v>
+        <v>119850872</v>
       </c>
       <c r="B11" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,38 +1722,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626602</v>
+        <v>626667</v>
       </c>
       <c r="R11" t="n">
-        <v>6897710</v>
+        <v>6897628</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119850449</v>
+        <v>119848797</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,47 +1843,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626682</v>
+        <v>626642</v>
       </c>
       <c r="R12" t="n">
-        <v>6897973</v>
+        <v>6897655</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1915,7 +1906,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1916,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119848811</v>
+        <v>119849763</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,46 +1959,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626637</v>
+        <v>626771</v>
       </c>
       <c r="R13" t="n">
-        <v>6897656</v>
+        <v>6897796</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2036,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119848698</v>
+        <v>119849022</v>
       </c>
       <c r="B14" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,38 +2067,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626565</v>
+        <v>626600</v>
       </c>
       <c r="R14" t="n">
-        <v>6897628</v>
+        <v>6897718</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2148,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,7 +2176,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119850843</v>
+        <v>119849031</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2218,17 +2209,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626698</v>
+        <v>626550</v>
       </c>
       <c r="R15" t="n">
-        <v>6897755</v>
+        <v>6897759</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,7 +2297,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119849799</v>
+        <v>119848698</v>
       </c>
       <c r="B16" t="n">
         <v>90545</v>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626805</v>
+        <v>626565</v>
       </c>
       <c r="R16" t="n">
-        <v>6897774</v>
+        <v>6897628</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119850872</v>
+        <v>119848811</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,50 +2421,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626667</v>
+        <v>626637</v>
       </c>
       <c r="R17" t="n">
-        <v>6897628</v>
+        <v>6897656</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -1943,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119849763</v>
+        <v>119849022</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,38 +1955,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626771</v>
+        <v>626600</v>
       </c>
       <c r="R13" t="n">
-        <v>6897796</v>
+        <v>6897718</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2018,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119849022</v>
+        <v>119849763</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2067,47 +2076,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626600</v>
+        <v>626771</v>
       </c>
       <c r="R14" t="n">
-        <v>6897718</v>
+        <v>6897796</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119848932</v>
+        <v>119848811</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626605</v>
+        <v>626637</v>
       </c>
       <c r="R2" t="n">
-        <v>6897688</v>
+        <v>6897656</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119850449</v>
+        <v>119848966</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,47 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626682</v>
+        <v>626602</v>
       </c>
       <c r="R3" t="n">
-        <v>6897973</v>
+        <v>6897710</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119849799</v>
+        <v>119849743</v>
       </c>
       <c r="B4" t="n">
-        <v>90545</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626805</v>
+        <v>626771</v>
       </c>
       <c r="R4" t="n">
-        <v>6897774</v>
+        <v>6897796</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1029,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119848807</v>
+        <v>119849022</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1062,17 +1053,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626637</v>
+        <v>626600</v>
       </c>
       <c r="R5" t="n">
-        <v>6897656</v>
+        <v>6897718</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119848727</v>
+        <v>119850449</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,38 +1153,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626573</v>
+        <v>626682</v>
       </c>
       <c r="R6" t="n">
-        <v>6897625</v>
+        <v>6897973</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119848966</v>
+        <v>119848727</v>
       </c>
       <c r="B7" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,21 +1278,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626602</v>
+        <v>626573</v>
       </c>
       <c r="R7" t="n">
-        <v>6897710</v>
+        <v>6897625</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119849743</v>
+        <v>119848932</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,38 +1386,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626771</v>
+        <v>626605</v>
       </c>
       <c r="R8" t="n">
-        <v>6897796</v>
+        <v>6897688</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119848788</v>
+        <v>119848797</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,47 +1507,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626654</v>
+        <v>626642</v>
       </c>
       <c r="R9" t="n">
-        <v>6897634</v>
+        <v>6897655</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1598,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119850843</v>
+        <v>119850872</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1631,17 +1640,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626698</v>
+        <v>626667</v>
       </c>
       <c r="R10" t="n">
-        <v>6897755</v>
+        <v>6897628</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1673,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119850872</v>
+        <v>119848698</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,44 +1740,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626667</v>
+        <v>626565</v>
       </c>
       <c r="R11" t="n">
         <v>6897628</v>
@@ -1794,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119848797</v>
+        <v>119848807</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,25 +1852,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1871,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626642</v>
+        <v>626637</v>
       </c>
       <c r="R12" t="n">
-        <v>6897655</v>
+        <v>6897656</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1906,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1916,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119849022</v>
+        <v>119849763</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,47 +1964,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626600</v>
+        <v>626771</v>
       </c>
       <c r="R13" t="n">
-        <v>6897718</v>
+        <v>6897796</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119849763</v>
+        <v>119849799</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,25 +2076,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626771</v>
+        <v>626805</v>
       </c>
       <c r="R14" t="n">
-        <v>6897796</v>
+        <v>6897774</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2297,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119848698</v>
+        <v>119850843</v>
       </c>
       <c r="B16" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2309,25 +2309,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626565</v>
+        <v>626698</v>
       </c>
       <c r="R16" t="n">
-        <v>6897628</v>
+        <v>6897755</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119848811</v>
+        <v>119848788</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,50 +2421,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626637</v>
+        <v>626654</v>
       </c>
       <c r="R17" t="n">
-        <v>6897656</v>
+        <v>6897634</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -1262,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119848727</v>
+        <v>119848932</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,38 +1274,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626573</v>
+        <v>626605</v>
       </c>
       <c r="R7" t="n">
-        <v>6897625</v>
+        <v>6897688</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119848932</v>
+        <v>119848727</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,47 +1395,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626605</v>
+        <v>626573</v>
       </c>
       <c r="R8" t="n">
-        <v>6897688</v>
+        <v>6897625</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119848797</v>
+        <v>119850872</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,38 +1507,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626642</v>
+        <v>626667</v>
       </c>
       <c r="R9" t="n">
-        <v>6897655</v>
+        <v>6897628</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1570,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119850872</v>
+        <v>119848797</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,47 +1628,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626667</v>
+        <v>626642</v>
       </c>
       <c r="R10" t="n">
-        <v>6897628</v>
+        <v>6897655</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119848811</v>
+        <v>119849031</v>
       </c>
       <c r="B2" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
+          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626637</v>
+        <v>626550</v>
       </c>
       <c r="R2" t="n">
-        <v>6897656</v>
+        <v>6897759</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119848966</v>
+        <v>119849743</v>
       </c>
       <c r="B3" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626602</v>
+        <v>626771</v>
       </c>
       <c r="R3" t="n">
-        <v>6897710</v>
+        <v>6897796</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119849743</v>
+        <v>119848811</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,37 +924,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626771</v>
+        <v>626637</v>
       </c>
       <c r="R4" t="n">
-        <v>6897796</v>
+        <v>6897656</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119849022</v>
+        <v>119850872</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1069,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626600</v>
+        <v>626667</v>
       </c>
       <c r="R5" t="n">
-        <v>6897718</v>
+        <v>6897628</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1262,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119848932</v>
+        <v>119848727</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,47 +1283,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626605</v>
+        <v>626573</v>
       </c>
       <c r="R7" t="n">
-        <v>6897688</v>
+        <v>6897625</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119848727</v>
+        <v>119849022</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,38 +1395,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626573</v>
+        <v>626600</v>
       </c>
       <c r="R8" t="n">
-        <v>6897625</v>
+        <v>6897718</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,7 +1504,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119850872</v>
+        <v>119850843</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1528,26 +1537,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626667</v>
+        <v>626698</v>
       </c>
       <c r="R9" t="n">
-        <v>6897628</v>
+        <v>6897755</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119848797</v>
+        <v>119848932</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,38 +1628,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626642</v>
+        <v>626605</v>
       </c>
       <c r="R10" t="n">
-        <v>6897655</v>
+        <v>6897688</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1691,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1710,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119848698</v>
+        <v>119848788</v>
       </c>
       <c r="B11" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,38 +1749,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626565</v>
+        <v>626654</v>
       </c>
       <c r="R11" t="n">
-        <v>6897628</v>
+        <v>6897634</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1803,7 +1821,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1831,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,10 +1858,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119848807</v>
+        <v>119849763</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,25 +1870,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1898,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626637</v>
+        <v>626771</v>
       </c>
       <c r="R12" t="n">
-        <v>6897656</v>
+        <v>6897796</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1915,7 +1933,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1970,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119849763</v>
+        <v>119849799</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,25 +1982,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626771</v>
+        <v>626805</v>
       </c>
       <c r="R13" t="n">
-        <v>6897796</v>
+        <v>6897774</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2064,10 +2082,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119849799</v>
+        <v>119848797</v>
       </c>
       <c r="B14" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,25 +2094,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2104,10 +2122,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626805</v>
+        <v>626642</v>
       </c>
       <c r="R14" t="n">
-        <v>6897774</v>
+        <v>6897655</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2139,7 +2157,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2167,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119849031</v>
+        <v>119848698</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,47 +2206,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626550</v>
+        <v>626565</v>
       </c>
       <c r="R15" t="n">
-        <v>6897759</v>
+        <v>6897628</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2260,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,7 +2306,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119850843</v>
+        <v>119848807</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2337,10 +2346,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626698</v>
+        <v>626637</v>
       </c>
       <c r="R16" t="n">
-        <v>6897755</v>
+        <v>6897656</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2372,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,10 +2418,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119848788</v>
+        <v>119848966</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,47 +2430,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626654</v>
+        <v>626602</v>
       </c>
       <c r="R17" t="n">
-        <v>6897634</v>
+        <v>6897710</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119849031</v>
+        <v>119870499</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>483</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
+          <t>Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626550</v>
+        <v>626602</v>
       </c>
       <c r="R2" t="n">
-        <v>6897759</v>
+        <v>6897691</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,27 +746,18 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:27</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:27</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119849743</v>
+        <v>119848966</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626771</v>
+        <v>626602</v>
       </c>
       <c r="R3" t="n">
-        <v>6897796</v>
+        <v>6897710</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +846,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +856,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119848811</v>
+        <v>119848727</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,46 +894,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626637</v>
+        <v>626573</v>
       </c>
       <c r="R4" t="n">
-        <v>6897656</v>
+        <v>6897625</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +953,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +963,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,59 +990,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119850872</v>
+        <v>119848797</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626667</v>
+        <v>626642</v>
       </c>
       <c r="R5" t="n">
-        <v>6897628</v>
+        <v>6897655</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,7 +1060,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1070,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,59 +1097,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119850449</v>
+        <v>119849729</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626682</v>
+        <v>626771</v>
       </c>
       <c r="R6" t="n">
-        <v>6897973</v>
+        <v>6897796</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1234,7 +1167,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1177,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,37 +1204,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119848727</v>
+        <v>119849502</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626573</v>
+        <v>626696</v>
       </c>
       <c r="R7" t="n">
-        <v>6897625</v>
+        <v>6897732</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1274,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1284,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,59 +1311,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119849022</v>
+        <v>119848698</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626600</v>
+        <v>626565</v>
       </c>
       <c r="R8" t="n">
-        <v>6897718</v>
+        <v>6897628</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1467,7 +1381,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1391,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,37 +1418,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119850843</v>
+        <v>119849799</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1544,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626698</v>
+        <v>626805</v>
       </c>
       <c r="R9" t="n">
-        <v>6897755</v>
+        <v>6897774</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1579,7 +1488,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1498,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,62 +1525,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119848932</v>
+        <v>119848811</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyran, Njurunda, Älgmyran, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626605</v>
+        <v>626637</v>
       </c>
       <c r="R10" t="n">
-        <v>6897688</v>
+        <v>6897656</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,7 +1604,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,7 +1614,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,12 +1644,7 @@
         <v>119848788</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,37 +1757,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119849763</v>
+        <v>119848807</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1898,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626771</v>
+        <v>626637</v>
       </c>
       <c r="R12" t="n">
-        <v>6897796</v>
+        <v>6897656</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1933,7 +1827,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1943,7 +1837,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,50 +1864,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119849799</v>
+        <v>119848932</v>
       </c>
       <c r="B13" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626805</v>
+        <v>626605</v>
       </c>
       <c r="R13" t="n">
-        <v>6897774</v>
+        <v>6897688</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2045,7 +1943,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,7 +1953,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,50 +1980,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119848797</v>
+        <v>119849022</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626642</v>
+        <v>626600</v>
       </c>
       <c r="R14" t="n">
-        <v>6897655</v>
+        <v>6897718</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2157,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2167,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2194,50 +2096,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119848698</v>
+        <v>119849031</v>
       </c>
       <c r="B15" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626565</v>
+        <v>626550</v>
       </c>
       <c r="R15" t="n">
-        <v>6897628</v>
+        <v>6897759</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2269,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,15 +2212,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119848807</v>
+        <v>119850449</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,17 +2240,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Brandstockmyran, Brandstockmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626637</v>
+        <v>626682</v>
       </c>
       <c r="R16" t="n">
-        <v>6897656</v>
+        <v>6897973</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2381,7 +2291,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2301,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,37 +2328,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119848966</v>
+        <v>119850843</v>
       </c>
       <c r="B17" t="n">
-        <v>90864</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2458,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626602</v>
+        <v>626698</v>
       </c>
       <c r="R17" t="n">
-        <v>6897710</v>
+        <v>6897755</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2493,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2503,7 +2408,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2530,15 +2435,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119870499</v>
+        <v>119850872</v>
       </c>
       <c r="B18" t="n">
-        <v>91193</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2546,37 +2446,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>483</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Älgmyran, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626602</v>
+        <v>626667</v>
       </c>
       <c r="R18" t="n">
-        <v>6897691</v>
+        <v>6897628</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2606,18 +2512,27 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2633,118 +2548,6 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>119849502</v>
-      </c>
-      <c r="B19" t="n">
-        <v>91258</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1339</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Brandticka</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Pycnoporellus fulgens</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>626696</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6897732</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Njurunda</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33746-2024 artfynd.xlsx
+++ b/artfynd/A 33746-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119870499</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848966</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848727</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848797</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849729</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849502</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848698</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849799</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1638,6 +1683,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848811</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1754,6 +1804,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848788</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1861,6 +1916,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848807</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1977,6 +2037,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848932</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849022</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2209,6 +2279,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849031</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2325,6 +2400,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850449</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2432,6 +2512,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850843</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2548,8 +2633,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850872</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>